--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFBB427-F298-45BE-BB64-ED443F878701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227DF309-1324-48C7-B4F3-F0E11E0EE557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Vocab</t>
   </si>
@@ -32,57 +32,6 @@
   </si>
   <si>
     <t>Contoh</t>
-  </si>
-  <si>
-    <t>Keen</t>
-  </si>
-  <si>
-    <t>Daft</t>
-  </si>
-  <si>
-    <t>A bit of alright</t>
-  </si>
-  <si>
-    <t>Chuffed</t>
-  </si>
-  <si>
-    <t>Gobsmacked</t>
-  </si>
-  <si>
-    <t>adjective</t>
-  </si>
-  <si>
-    <t>idiom</t>
-  </si>
-  <si>
-    <t>Sangat tertarik, bersemangat, atau tajam secara intelektual.</t>
-  </si>
-  <si>
-    <t>Silly; agak konyol atau bodoh tapi dalam konteks yang jenaka/ringan.</t>
-  </si>
-  <si>
-    <t>Ungkapan kolokial untuk sesuatu atau seseorang yang sangat menarik atau memuaskan.</t>
-  </si>
-  <si>
-    <t>Sangat senang atau puas atas suatu pencapaian atau kabar baik.</t>
-  </si>
-  <si>
-    <t>Sangat terkejut atau terpana hingga tidak bisa berkata-kata.</t>
-  </si>
-  <si>
-    <t>He's very keen on learning classical piano.</t>
-  </si>
-  <si>
-    <t>Don't be daft, of course you can pass the exam!</t>
-  </si>
-  <si>
-    <t>That new suit you wore to the presentation is a bit of alright!</t>
-  </si>
-  <si>
-    <t>I was absolutely chuffed when I received the top marks.</t>
-  </si>
-  <si>
-    <t>She was completely gobsmacked when she heard the news.</t>
   </si>
   <si>
     <t>Andre</t>
@@ -453,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -475,83 +424,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227DF309-1324-48C7-B4F3-F0E11E0EE557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9990129C-C15F-434D-B606-A3A72D668BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>Vocab</t>
   </si>
@@ -35,6 +35,15 @@
   </si>
   <si>
     <t>Andre</t>
+  </si>
+  <si>
+    <t>jkrgn</t>
+  </si>
+  <si>
+    <t>ghdf</t>
+  </si>
+  <si>
+    <t>sfg</t>
   </si>
 </sst>
 </file>
@@ -402,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -433,6 +442,20 @@
         <v>4</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9990129C-C15F-434D-B606-A3A72D668BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B590DC9-A5C1-4A59-A644-0A51EA129DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Vocab</t>
   </si>
@@ -34,23 +34,615 @@
     <t>Contoh</t>
   </si>
   <si>
-    <t>Andre</t>
-  </si>
-  <si>
-    <t>jkrgn</t>
-  </si>
-  <si>
-    <t>ghdf</t>
-  </si>
-  <si>
-    <t>sfg</t>
+    <t>Massive, crushing ……</t>
+  </si>
+  <si>
+    <t>…… besar yang menghancurkan</t>
+  </si>
+  <si>
+    <t>A quick aside about ….</t>
+  </si>
+  <si>
+    <t>Sedikit informasi tentang …</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The company is facing a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>massive, crushing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> debt after the market crashed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Recently</t>
+  </si>
+  <si>
+    <t>Baru-baru ini</t>
+  </si>
+  <si>
+    <t>Wealthy</t>
+  </si>
+  <si>
+    <t>Kaya</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">He comes from a very </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wealthy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> family in London.</t>
+    </r>
+  </si>
+  <si>
+    <t>Better than he</t>
+  </si>
+  <si>
+    <t>Selain dia / Lebih baik dari dia</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">There is no one who can lead this club </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>better than he</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Rather annoying</t>
+  </si>
+  <si>
+    <t>Sangat/agak mengganggu</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The loud noise outside is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rather annoying</t>
+    </r>
+  </si>
+  <si>
+    <t>Precisely</t>
+  </si>
+  <si>
+    <t>Tepat sekali</t>
+  </si>
+  <si>
+    <r>
+      <t>So we need to cut costs?" "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Precisely</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>An Exquisite ………</t>
+  </si>
+  <si>
+    <t>….. yang manis / luar biasa indah</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">She wore </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>an exquisite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dress to the gala.</t>
+    </r>
+  </si>
+  <si>
+    <t>I demand</t>
+  </si>
+  <si>
+    <t>Aku meminta / menuntut</t>
+  </si>
+  <si>
+    <r>
+      <t>I demand</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> an explanation for this mistake.</t>
+    </r>
+  </si>
+  <si>
+    <t>Restorative</t>
+  </si>
+  <si>
+    <t>…, comrade</t>
+  </si>
+  <si>
+    <t>…, kawan</t>
+  </si>
+  <si>
+    <t>I shan’t</t>
+  </si>
+  <si>
+    <t>Aku tidak mau / tidak akan</t>
+  </si>
+  <si>
+    <r>
+      <t>I shan’t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tolerate any laziness in this team.</t>
+    </r>
+  </si>
+  <si>
+    <t>Magnificent</t>
+  </si>
+  <si>
+    <t>Luar Biasa / Indah</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The view from the top of the mountain was </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>magnificent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Prior to this</t>
+  </si>
+  <si>
+    <t>Sebelum ini</t>
+  </si>
+  <si>
+    <r>
+      <t>Prior to this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, I had never studied international tax.</t>
+    </r>
+  </si>
+  <si>
+    <t>Seeking to determine</t>
+  </si>
+  <si>
+    <t>Berusaha untuk menentukan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>seeking to determine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the best strategy for the competition.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">As </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a quick aside about</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the methodology, we utilized a randomized sampling approach to ensure objectivity.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Recently,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> empirical studies have shown a significant shift in corporate taxation strategies.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The central bank introduced </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>restorative</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> economic measures to stabilize the fluctuating currency.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cemilan / sesuatu yang memulihkan tenaga / memulihkan / memperbaiki</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We must consolidate our resources to achieve the quarterly objectives, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>comrades</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Practicable</t>
+  </si>
+  <si>
+    <t>Dapat diterapkan / Layak</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The committee must evaluate whether the proposed legal reform is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>practicable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> under current conditions.</t>
+    </r>
+  </si>
+  <si>
+    <t>is the outpouring</t>
+  </si>
+  <si>
+    <t>Merupakan perwujudan / curahan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The sudden surge in innovation </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>is the outpouring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of massive investments in research and development.</t>
+    </r>
+  </si>
+  <si>
+    <t>equally important</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implementing the fiscal policy is crucial, but monitoring its execution is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>equally important</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sama pentingnya</t>
+  </si>
+  <si>
+    <t>at the dawn of   ….</t>
+  </si>
+  <si>
+    <t>Pada awal mula…</t>
+  </si>
+  <si>
+    <t>The global economic landscape shifted drastically at the dawn of the Industrial Revolution.</t>
+  </si>
+  <si>
+    <t>to fashion</t>
+  </si>
+  <si>
+    <t>Untuk merancang / membentuk</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Policymakers met to discuss how </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>to fashion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a comprehensive treaty on environmental protection.</t>
+    </r>
+  </si>
+  <si>
+    <t>sum up an ….</t>
+  </si>
+  <si>
+    <t>Merangkum suatu…</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">It is challenging to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sum up an</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intricate economic theory within a single executive summary.</t>
+    </r>
+  </si>
+  <si>
+    <t>Intricate</t>
+  </si>
+  <si>
+    <t>Rumit</t>
+  </si>
+  <si>
+    <t>Order a slice of cake or one of the intricate desserts.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,6 +657,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFE8E8E8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -102,10 +700,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,8 +1014,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.6328125" customWidth="1"/>
+    <col min="3" max="3" width="42.81640625" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -432,28 +1040,242 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="35" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA793EA-FBF7-4056-BC86-0D88E98B961D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A26403D-A869-4D24-B338-1DE8C9BC1F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t>Vocab</t>
   </si>
@@ -941,13 +941,262 @@
   </si>
   <si>
     <t>Precedented</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The government's decision to intervene in the market was entirely </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>precedented</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by similar actions taken during the previous decade</t>
+    </r>
+  </si>
+  <si>
+    <t>Didahului</t>
+  </si>
+  <si>
+    <t>Entirely</t>
+  </si>
+  <si>
+    <t>Sepenuhnya</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Their backgrounds are </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>entirely</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> different</t>
+    </r>
+  </si>
+  <si>
+    <t>Take Charge</t>
+  </si>
+  <si>
+    <t>Mengendali</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">With the deadline approaching rapidly, the chairman decided to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>take charge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the project to ensure everything ran smoothly</t>
+    </r>
+  </si>
+  <si>
+    <t>Procratinaste</t>
+  </si>
+  <si>
+    <t>Menunda-nunda</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Stop </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>procrastinating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on setting up your retirement fund. The earlier you start, the more your money grows</t>
+    </r>
+  </si>
+  <si>
+    <t>Detrimental</t>
+  </si>
+  <si>
+    <t>Sangat merugikan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Piling up high-interest credit card debt is highly </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>detrimental</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to your long-term financial health</t>
+    </r>
+  </si>
+  <si>
+    <t>Pile Up</t>
+  </si>
+  <si>
+    <t>Menumpuk</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">He kept delaying his revision, and now the assignments are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>piling up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> right before the exam week</t>
+    </r>
+  </si>
+  <si>
+    <t>Engage</t>
+  </si>
+  <si>
+    <t>Terlibat</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">As a leader, it is crucial to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>engage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in open discussions with your team members to align everyone's goals</t>
+    </r>
+  </si>
+  <si>
+    <t>Conspicuous</t>
+  </si>
+  <si>
+    <t>Mencolok</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Many people fall into the trap of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>conspicuous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> consumption, buying luxury items just to impress others, which ruins their savings</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -962,12 +1211,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFE8E8E8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -987,6 +1230,17 @@
     <font>
       <sz val="9"/>
       <color rgb="FF1D2A57"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1026,21 +1280,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1346,291 +1599,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.6328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5"/>
-    <col min="3" max="3" width="42.81640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="73.26953125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="27.6328125" customWidth="1"/>
+    <col min="3" max="3" width="42.81640625" customWidth="1"/>
+    <col min="4" max="4" width="73.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="5" t="s">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+      <c r="A17" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+      <c r="A18" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
+      <c r="A19" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+      <c r="A20" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
+      <c r="A21" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+      <c r="A22" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="35" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="7" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+      <c r="A24" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="5" t="s">
+      <c r="A25" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1660,7 +1911,7 @@
       <c r="A28" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>83</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -1767,57 +2018,57 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" t="s">
         <v>112</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" t="s">
         <v>113</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="5" t="s">
+      <c r="A39" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="5" t="s">
+      <c r="A41" t="s">
         <v>121</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" t="s">
         <v>122</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="2" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="s">
+      <c r="A42" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" t="s">
         <v>126</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="2" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1910,13 +2161,13 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="5" t="s">
+      <c r="A51" t="s">
         <v>151</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" t="s">
         <v>152</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="2" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1932,22 +2183,106 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="5" t="s">
+      <c r="A53" t="s">
         <v>157</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" t="s">
         <v>158</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="2" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="5" t="s">
+      <c r="A54" t="s">
         <v>160</v>
+      </c>
+      <c r="C54" t="s">
+        <v>162</v>
+      </c>
+      <c r="D54" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C55" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" t="s">
+        <v>167</v>
+      </c>
+      <c r="D56" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" t="s">
+        <v>170</v>
+      </c>
+      <c r="D57" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>178</v>
+      </c>
+      <c r="C60" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>181</v>
+      </c>
+      <c r="C61" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A26403D-A869-4D24-B338-1DE8C9BC1F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B77871-7144-4966-B27D-F27F5AE1C055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
   <si>
     <t>Vocab</t>
   </si>
@@ -1189,6 +1189,175 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> consumption, buying luxury items just to impress others, which ruins their savings</t>
+    </r>
+  </si>
+  <si>
+    <t>Preferably</t>
+  </si>
+  <si>
+    <t>Idealnya,</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You should clear your high-interest debts as soon as possible, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>preferably</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> before you start allocated money for aggressive investments</t>
+    </r>
+  </si>
+  <si>
+    <t>Acquire</t>
+  </si>
+  <si>
+    <t>Mendapatkan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Financial literacy is not something you are born with; it is an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>acquired</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> taste and skill that comes from continuous reading and practice</t>
+    </r>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>Terus-menerus</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Success in mastering difficult subjects like physics or calculus is the result of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>continuous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> practice, not just cramming the night before the exam</t>
+    </r>
+  </si>
+  <si>
+    <t>Cram</t>
+  </si>
+  <si>
+    <t>Menyumpal</t>
+  </si>
+  <si>
+    <t>cram a suitcase with clothes</t>
+  </si>
+  <si>
+    <t>Cramming</t>
+  </si>
+  <si>
+    <t>Strategi berisiko, sering kali gagal</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">By setting minor deadlines throughout the month, the team avoided </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cramming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> all the report writing into the final weekend</t>
+    </r>
+  </si>
+  <si>
+    <t>Thus</t>
+  </si>
+  <si>
+    <t>Dengan demikian,</t>
+  </si>
+  <si>
+    <r>
+      <t>The data shows a continuous rise in inflation over the past three quarters. T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, the central bank is highly likely to increase interest rates next month</t>
     </r>
   </si>
 </sst>
@@ -1196,7 +1365,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1244,6 +1413,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1280,7 +1454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1295,6 +1469,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1599,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.6328125" customWidth="1"/>
@@ -2281,6 +2456,72 @@
         <v>183</v>
       </c>
     </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" t="s">
+        <v>188</v>
+      </c>
+      <c r="D63" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>190</v>
+      </c>
+      <c r="C64" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65" t="s">
+        <v>194</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>196</v>
+      </c>
+      <c r="C66" t="s">
+        <v>197</v>
+      </c>
+      <c r="D66" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" t="s">
+        <v>200</v>
+      </c>
+      <c r="D67" t="s">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B77871-7144-4966-B27D-F27F5AE1C055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18EF527-72FF-42E8-93CA-2F53BB2D3EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="216">
   <si>
     <t>Vocab</t>
   </si>
@@ -40,12 +40,6 @@
     <t>…… besar yang menghancurkan</t>
   </si>
   <si>
-    <t>A quick aside about ….</t>
-  </si>
-  <si>
-    <t>Sedikit informasi tentang …</t>
-  </si>
-  <si>
     <t>Recently</t>
   </si>
   <si>
@@ -58,12 +52,6 @@
     <t>Kaya</t>
   </si>
   <si>
-    <t>Better than he</t>
-  </si>
-  <si>
-    <t>Selain dia / Lebih baik dari dia</t>
-  </si>
-  <si>
     <t>Rather annoying</t>
   </si>
   <si>
@@ -115,12 +103,6 @@
     <t>Sebelum ini</t>
   </si>
   <si>
-    <t>Seeking to determine</t>
-  </si>
-  <si>
-    <t>Berusaha untuk menentukan</t>
-  </si>
-  <si>
     <t>Cemilan / sesuatu yang memulihkan tenaga / memulihkan / memperbaiki</t>
   </si>
   <si>
@@ -142,15 +124,6 @@
     <t>Sama pentingnya</t>
   </si>
   <si>
-    <t>at the dawn of   ….</t>
-  </si>
-  <si>
-    <t>Pada awal mula…</t>
-  </si>
-  <si>
-    <t>The global economic landscape shifted drastically at the dawn of the Industrial Revolution.</t>
-  </si>
-  <si>
     <t>to fashion</t>
   </si>
   <si>
@@ -190,18 +163,12 @@
     <t>The company is facing a massive, crushing debt after the market crashed.</t>
   </si>
   <si>
-    <t>As a quick aside about the methodology, we utilized a randomized sampling approach to ensure objectivity.</t>
-  </si>
-  <si>
     <t>Recently, empirical studies have shown a significant shift in corporate taxation strategies.</t>
   </si>
   <si>
     <t>He comes from a very wealthy family in London.</t>
   </si>
   <si>
-    <t>There is no one who can lead this club better than he.</t>
-  </si>
-  <si>
     <t>The loud noise outside is rather annoying</t>
   </si>
   <si>
@@ -229,9 +196,6 @@
     <t>Prior to this, I had never studied international tax.</t>
   </si>
   <si>
-    <t>We are seeking to determine the best strategy for the competition.</t>
-  </si>
-  <si>
     <t>The committee must evaluate whether the proposed legal reform is practicable under current conditions.</t>
   </si>
   <si>
@@ -314,27 +278,6 @@
     </r>
   </si>
   <si>
-    <t>Within The field of economics</t>
-  </si>
-  <si>
-    <t>Di dalam bidang ekonomi</t>
-  </si>
-  <si>
-    <r>
-      <t>Within the field of economics</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, the concept of the 'invisible hand' remains highly influential.</t>
-    </r>
-  </si>
-  <si>
     <t>Put forth idea</t>
   </si>
   <si>
@@ -367,38 +310,6 @@
     </r>
   </si>
   <si>
-    <t>Mutual self-interests</t>
-  </si>
-  <si>
-    <t>Kepentingan bersama</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">International trade deals are inherently sustained by the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>mutual self-interests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of the participating nations.</t>
-    </r>
-  </si>
-  <si>
     <t>Numerous</t>
   </si>
   <si>
@@ -452,25 +363,89 @@
     </r>
   </si>
   <si>
-    <t>Remain in balance</t>
-  </si>
-  <si>
-    <t>Tetap berada dalam kondisi seimbang</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">For a market to function efficiently, supply and demand must </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>remain in balance</t>
+    <t>fruitfully</t>
+  </si>
+  <si>
+    <t>Secara produktif / Memberikan hasil</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The research team spent the semester </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>fruitfully</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> analyzing the census data.</t>
+    </r>
+  </si>
+  <si>
+    <t>gains</t>
+  </si>
+  <si>
+    <t>Keuntungan / Pertumbuhan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The agricultural sector reported substantial productivity </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gains</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> following the technological upgrade.</t>
+    </r>
+  </si>
+  <si>
+    <t>Piece of work</t>
+  </si>
+  <si>
+    <t>Hasil karya / Dokumen kerja</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The comprehensive annual report is an exceptionally meticulous </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>piece of work</t>
     </r>
     <r>
       <rPr>
@@ -484,121 +459,239 @@
     </r>
   </si>
   <si>
-    <t>fruitfully</t>
-  </si>
-  <si>
-    <t>Secara produktif / Memberikan hasil</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The research team spent the semester </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>fruitfully</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> analyzing the census data.</t>
-    </r>
-  </si>
-  <si>
-    <t>outlined the concept</t>
-  </si>
-  <si>
-    <t>Menguraikan konsep</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The keynote speaker clearly </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>outlined the concept</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of sustainable corporate governance.</t>
-    </r>
-  </si>
-  <si>
-    <t>gains</t>
-  </si>
-  <si>
-    <t>Keuntungan / Pertumbuhan</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The agricultural sector reported substantial productivity </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>gains</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> following the technological upgrade.</t>
-    </r>
-  </si>
-  <si>
-    <t>Piece of work</t>
-  </si>
-  <si>
-    <t>Hasil karya / Dokumen kerja</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The comprehensive annual report is an exceptionally meticulous </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>piece of work</t>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>Tahunan</t>
+  </si>
+  <si>
+    <t>They spent their annual holiday on a yacht in the Caribbean.</t>
+  </si>
+  <si>
+    <t>Exceptionally</t>
+  </si>
+  <si>
+    <t>Sangat</t>
+  </si>
+  <si>
+    <t>He is an exceptionally talented teacher.</t>
+  </si>
+  <si>
+    <t>Meticulous</t>
+  </si>
+  <si>
+    <t>Teliti</t>
+  </si>
+  <si>
+    <t>Many hours of meticulous preparation have gone into writing the book.</t>
+  </si>
+  <si>
+    <t>Substantial</t>
+  </si>
+  <si>
+    <t>Signifikan</t>
+  </si>
+  <si>
+    <t>The findings show a substantial difference between the opinions of men and women.</t>
+  </si>
+  <si>
+    <t>Inherently</t>
+  </si>
+  <si>
+    <t>She felt that the system was inherently unfair and unequal.</t>
+  </si>
+  <si>
+    <t>Secara inheren / pada dasarnya</t>
+  </si>
+  <si>
+    <t>Yours sincerel</t>
+  </si>
+  <si>
+    <t>Hormat saya - Jika nama penerima diketahui</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[Penutup korespondensi bisnis] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yours sincerely</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, Aryasatya Keandre</t>
+    </r>
+  </si>
+  <si>
+    <t>Yours faithfully</t>
+  </si>
+  <si>
+    <t>Hormat saya - Jika nama penerima tidak diketahui</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[Penutup surat resmi resmi] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yours faithfully</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, Executive Committee Representative.</t>
+    </r>
+  </si>
+  <si>
+    <t>Whether …..</t>
+  </si>
+  <si>
+    <t>Apakah….</t>
+  </si>
+  <si>
+    <t>The primary issue is whether the central bank will raise interest rates this quarter.</t>
+  </si>
+  <si>
+    <t>Intricate game</t>
+  </si>
+  <si>
+    <t>Permainan/interaksi yang rumit</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Geopolitics is an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intricate game</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of diplomacy, economics, and military power.</t>
+    </r>
+  </si>
+  <si>
+    <t>Contests of….</t>
+  </si>
+  <si>
+    <t>Persaingan / Kompetisi mengenai…</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In corporate markets, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>contests of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> technological innovation dictate industry leadership.</t>
+    </r>
+  </si>
+  <si>
+    <t>….are after</t>
+  </si>
+  <si>
+    <t>…sedang mengincar / berusaha mengejar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Venture capitalists </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>are after</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> high-growth startups with proprietary technology.</t>
+    </r>
+  </si>
+  <si>
+    <t>….after all,</t>
+  </si>
+  <si>
+    <t>…., bagaimanapun juga / pada akhirnya</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We must prioritize long-term sustainability; short-term profit is transient, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>after all</t>
     </r>
     <r>
       <rPr>
@@ -612,239 +705,806 @@
     </r>
   </si>
   <si>
-    <t>Annual</t>
-  </si>
-  <si>
-    <t>Tahunan</t>
-  </si>
-  <si>
-    <t>They spent their annual holiday on a yacht in the Caribbean.</t>
-  </si>
-  <si>
-    <t>Exceptionally</t>
-  </si>
-  <si>
-    <t>Sangat</t>
-  </si>
-  <si>
-    <t>He is an exceptionally talented teacher.</t>
-  </si>
-  <si>
-    <t>Meticulous</t>
-  </si>
-  <si>
-    <t>Teliti</t>
-  </si>
-  <si>
-    <t>Many hours of meticulous preparation have gone into writing the book.</t>
-  </si>
-  <si>
-    <t>Substantial</t>
-  </si>
-  <si>
-    <t>Signifikan</t>
-  </si>
-  <si>
-    <t>The findings show a substantial difference between the opinions of men and women.</t>
-  </si>
-  <si>
-    <t>Inherently</t>
-  </si>
-  <si>
-    <t>She felt that the system was inherently unfair and unequal.</t>
-  </si>
-  <si>
-    <t>Secara inheren / pada dasarnya</t>
-  </si>
-  <si>
-    <t>Yours sincerel</t>
-  </si>
-  <si>
-    <t>Hormat saya - Jika nama penerima diketahui</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[Penutup korespondensi bisnis] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Yours sincerely</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, Aryasatya Keandre</t>
-    </r>
-  </si>
-  <si>
-    <t>Yours faithfully</t>
-  </si>
-  <si>
-    <t>Hormat saya - Jika nama penerima tidak diketahui</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[Penutup surat resmi resmi] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Yours faithfully</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, Executive Committee Representative.</t>
-    </r>
-  </si>
-  <si>
-    <t>Whether …..</t>
-  </si>
-  <si>
-    <t>Apakah….</t>
-  </si>
-  <si>
-    <t>The primary issue is whether the central bank will raise interest rates this quarter.</t>
-  </si>
-  <si>
-    <t>Intricate game</t>
-  </si>
-  <si>
-    <t>Permainan/interaksi yang rumit</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Geopolitics is an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>intricate game</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of diplomacy, economics, and military power.</t>
-    </r>
-  </si>
-  <si>
-    <t>Contests of….</t>
-  </si>
-  <si>
-    <t>Persaingan / Kompetisi mengenai…</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">In corporate markets, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>contests of</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> technological innovation dictate industry leadership.</t>
-    </r>
-  </si>
-  <si>
-    <t>….are after</t>
-  </si>
-  <si>
-    <t>…sedang mengincar / berusaha mengejar</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Venture capitalists </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>are after</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> high-growth startups with proprietary technology.</t>
-    </r>
-  </si>
-  <si>
-    <t>is intriguing to the economist</t>
-  </si>
-  <si>
-    <t>Menarik perhatian para ekonom</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The paradox of high inflation accompanied by low unemployment </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>is intriguing to the economist</t>
+    <t>transient</t>
+  </si>
+  <si>
+    <t>Sementara</t>
+  </si>
+  <si>
+    <t>The city has a large transient population (= many people who are living in it only temporarily).</t>
+  </si>
+  <si>
+    <t>Could boast</t>
+  </si>
+  <si>
+    <t>Dapat membanggakan / Memiliki keunggulan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rior to the recession, the nation </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>could boast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> an unprecedented level of employment stability.</t>
+    </r>
+  </si>
+  <si>
+    <t>Recession</t>
+  </si>
+  <si>
+    <t>Resesi</t>
+  </si>
+  <si>
+    <t>For the second time in ten years, the government has driven the economy into deep and damaging recession.</t>
+  </si>
+  <si>
+    <t>Precedented</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The government's decision to intervene in the market was entirely </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>precedented</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by similar actions taken during the previous decade</t>
+    </r>
+  </si>
+  <si>
+    <t>Didahului</t>
+  </si>
+  <si>
+    <t>Entirely</t>
+  </si>
+  <si>
+    <t>Sepenuhnya</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Their backgrounds are </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>entirely</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> different</t>
+    </r>
+  </si>
+  <si>
+    <t>Take Charge</t>
+  </si>
+  <si>
+    <t>Mengendali</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">With the deadline approaching rapidly, the chairman decided to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>take charge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of the project to ensure everything ran smoothly</t>
+    </r>
+  </si>
+  <si>
+    <t>Procratinaste</t>
+  </si>
+  <si>
+    <t>Menunda-nunda</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Stop </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>procrastinating</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on setting up your retirement fund. The earlier you start, the more your money grows</t>
+    </r>
+  </si>
+  <si>
+    <t>Detrimental</t>
+  </si>
+  <si>
+    <t>Sangat merugikan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Piling up high-interest credit card debt is highly </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>detrimental</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to your long-term financial health</t>
+    </r>
+  </si>
+  <si>
+    <t>Pile Up</t>
+  </si>
+  <si>
+    <t>Menumpuk</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">He kept delaying his revision, and now the assignments are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>piling up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> right before the exam week</t>
+    </r>
+  </si>
+  <si>
+    <t>Engage</t>
+  </si>
+  <si>
+    <t>Terlibat</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">As a leader, it is crucial to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>engage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in open discussions with your team members to align everyone's goals</t>
+    </r>
+  </si>
+  <si>
+    <t>Conspicuous</t>
+  </si>
+  <si>
+    <t>Mencolok</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Many people fall into the trap of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>conspicuous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> consumption, buying luxury items just to impress others, which ruins their savings</t>
+    </r>
+  </si>
+  <si>
+    <t>Preferably</t>
+  </si>
+  <si>
+    <t>Idealnya,</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">You should clear your high-interest debts as soon as possible, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>preferably</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> before you start allocated money for aggressive investments</t>
+    </r>
+  </si>
+  <si>
+    <t>Acquire</t>
+  </si>
+  <si>
+    <t>Mendapatkan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Financial literacy is not something you are born with; it is an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>acquired</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> taste and skill that comes from continuous reading and practice</t>
+    </r>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>Terus-menerus</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Success in mastering difficult subjects like physics or calculus is the result of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>continuous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> practice, not just cramming the night before the exam</t>
+    </r>
+  </si>
+  <si>
+    <t>Cram</t>
+  </si>
+  <si>
+    <t>Menyumpal</t>
+  </si>
+  <si>
+    <t>cram a suitcase with clothes</t>
+  </si>
+  <si>
+    <t>Cramming</t>
+  </si>
+  <si>
+    <t>Strategi berisiko, sering kali gagal</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">By setting minor deadlines throughout the month, the team avoided </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cramming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> all the report writing into the final weekend</t>
+    </r>
+  </si>
+  <si>
+    <t>Thus</t>
+  </si>
+  <si>
+    <t>Dengan demikian,</t>
+  </si>
+  <si>
+    <r>
+      <t>The data shows a continuous rise in inflation over the past three quarters. T</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, the central bank is highly likely to increase interest rates next month</t>
+    </r>
+  </si>
+  <si>
+    <t>Encourage</t>
+  </si>
+  <si>
+    <t>Mendorong untuk melakukan sesuatu</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The teacher </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>encourages</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> her students to ask questions during the class</t>
+    </r>
+  </si>
+  <si>
+    <t>Accomplish</t>
+  </si>
+  <si>
+    <t>Mencampai</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">With hard work and discipline, you can </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>accomplish</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> any goals you set</t>
+    </r>
+  </si>
+  <si>
+    <t>Devote</t>
+  </si>
+  <si>
+    <t>Mendedikasikan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The first floor of the museum </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>is devoted to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ancient Indonesian history</t>
+    </r>
+  </si>
+  <si>
+    <t>Burden</t>
+  </si>
+  <si>
+    <t>Beban</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Carrying the secret became a heavy psychological </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>burden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for her</t>
+    </r>
+  </si>
+  <si>
+    <t>Inherit</t>
+  </si>
+  <si>
+    <t>Mewarisi</t>
+  </si>
+  <si>
+    <t>Falter</t>
+  </si>
+  <si>
+    <t>Bimbang</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The company's initial plans began to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>falter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> due to poor management </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Merriam-Webster</t>
+    </r>
+  </si>
+  <si>
+    <t>Agile</t>
+  </si>
+  <si>
+    <t>Tangkas</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">She possesses an extraordinarily </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>agile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mind, allowing her to solve complex puzzles in seconds</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Having </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inherited</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a heavily leveraged corporate entity, the young CEO was immediately forced to restructure the company’s outstanding debts to avert imminent bankruptcy</t>
+    </r>
+  </si>
+  <si>
+    <t>Avert</t>
+  </si>
+  <si>
+    <t>Mencegah</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Diplomatic talks were held to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>avert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a potential conflict between the two nations</t>
+    </r>
+  </si>
+  <si>
+    <t>Thoroughly</t>
+  </si>
+  <si>
+    <t>Secara menyeluruh</t>
+  </si>
+  <si>
+    <t>Overwhelming</t>
+  </si>
+  <si>
+    <t>Membebani</t>
+  </si>
+  <si>
+    <t>Dreadfully</t>
+  </si>
+  <si>
+    <t>Sangat buruk</t>
+  </si>
+  <si>
+    <t>Pique</t>
+  </si>
+  <si>
+    <t>Membangkitkan</t>
+  </si>
+  <si>
+    <t>Esoteric</t>
+  </si>
+  <si>
+    <t>Sesuatu yang hanya dipahami oleh segelintir orang</t>
+  </si>
+  <si>
+    <t>Coverage</t>
+  </si>
+  <si>
+    <t>Cakupan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The regulatory compliance framework imposed by the central bank was so </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thoroughly</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> complex that small-scale fintech startups found the initial auditing process utterly </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>overwhelming</t>
     </r>
     <r>
       <rPr>
@@ -858,93 +1518,14 @@
     </r>
   </si>
   <si>
-    <t>….after all,</t>
-  </si>
-  <si>
-    <t>…., bagaimanapun juga / pada akhirnya</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">We must prioritize long-term sustainability; short-term profit is transient, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>after all</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>transient</t>
-  </si>
-  <si>
-    <t>Sementara</t>
-  </si>
-  <si>
-    <t>The city has a large transient population (= many people who are living in it only temporarily).</t>
-  </si>
-  <si>
-    <t>Could boast</t>
-  </si>
-  <si>
-    <t>Dapat membanggakan / Memiliki keunggulan</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">rior to the recession, the nation </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>could boast</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> an unprecedented level of employment stability.</t>
-    </r>
-  </si>
-  <si>
-    <t>Recession</t>
-  </si>
-  <si>
-    <t>Resesi</t>
-  </si>
-  <si>
-    <t>For the second time in ten years, the government has driven the economy into deep and damaging recession.</t>
-  </si>
-  <si>
-    <t>Precedented</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The government's decision to intervene in the market was entirely </t>
+    <t>Impose</t>
+  </si>
+  <si>
+    <t>Memaksa</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The government decided to </t>
     </r>
     <r>
       <rPr>
@@ -953,411 +1534,43 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>precedented</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by similar actions taken during the previous decade</t>
-    </r>
-  </si>
-  <si>
-    <t>Didahului</t>
-  </si>
-  <si>
-    <t>Entirely</t>
-  </si>
-  <si>
-    <t>Sepenuhnya</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Their backgrounds are </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>entirely</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> different</t>
-    </r>
-  </si>
-  <si>
-    <t>Take Charge</t>
-  </si>
-  <si>
-    <t>Mengendali</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">With the deadline approaching rapidly, the chairman decided to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>take charge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of the project to ensure everything ran smoothly</t>
-    </r>
-  </si>
-  <si>
-    <t>Procratinaste</t>
-  </si>
-  <si>
-    <t>Menunda-nunda</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Stop </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>procrastinating</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on setting up your retirement fund. The earlier you start, the more your money grows</t>
-    </r>
-  </si>
-  <si>
-    <t>Detrimental</t>
-  </si>
-  <si>
-    <t>Sangat merugikan</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Piling up high-interest credit card debt is highly </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>detrimental</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to your long-term financial health</t>
-    </r>
-  </si>
-  <si>
-    <t>Pile Up</t>
-  </si>
-  <si>
-    <t>Menumpuk</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">He kept delaying his revision, and now the assignments are </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>piling up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> right before the exam week</t>
-    </r>
-  </si>
-  <si>
-    <t>Engage</t>
-  </si>
-  <si>
-    <t>Terlibat</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">As a leader, it is crucial to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>engage</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in open discussions with your team members to align everyone's goals</t>
-    </r>
-  </si>
-  <si>
-    <t>Conspicuous</t>
-  </si>
-  <si>
-    <t>Mencolok</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Many people fall into the trap of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>conspicuous</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> consumption, buying luxury items just to impress others, which ruins their savings</t>
-    </r>
-  </si>
-  <si>
-    <t>Preferably</t>
-  </si>
-  <si>
-    <t>Idealnya,</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">You should clear your high-interest debts as soon as possible, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>preferably</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> before you start allocated money for aggressive investments</t>
-    </r>
-  </si>
-  <si>
-    <t>Acquire</t>
-  </si>
-  <si>
-    <t>Mendapatkan</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Financial literacy is not something you are born with; it is an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>acquired</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> taste and skill that comes from continuous reading and practice</t>
-    </r>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>Terus-menerus</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Success in mastering difficult subjects like physics or calculus is the result of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>continuous</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> practice, not just cramming the night before the exam</t>
-    </r>
-  </si>
-  <si>
-    <t>Cram</t>
-  </si>
-  <si>
-    <t>Menyumpal</t>
-  </si>
-  <si>
-    <t>cram a suitcase with clothes</t>
-  </si>
-  <si>
-    <t>Cramming</t>
-  </si>
-  <si>
-    <t>Strategi berisiko, sering kali gagal</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">By setting minor deadlines throughout the month, the team avoided </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cramming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> all the report writing into the final weekend</t>
-    </r>
-  </si>
-  <si>
-    <t>Thus</t>
-  </si>
-  <si>
-    <t>Dengan demikian,</t>
-  </si>
-  <si>
-    <r>
-      <t>The data shows a continuous rise in inflation over the past three quarters. T</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>hus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, the central bank is highly likely to increase interest rates next month</t>
+      <t>impose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a new tax on luxury vehicles</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The researcher's unorthodox hypothesis regarding quantum entanglement managed to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pique</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the curiosity of the global scientific community, prompting further peer-reviewed investigations.</t>
     </r>
   </si>
 </sst>
@@ -1389,14 +1602,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF1D2A57"/>
       <name val="Arial"/>
@@ -1415,6 +1620,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1454,22 +1665,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1774,7 +1984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.6328125" customWidth="1"/>
@@ -1783,16 +1993,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1804,7 +2014,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1815,7 +2025,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1826,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1837,7 +2047,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1848,7 +2058,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1859,7 +2069,7 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1870,7 +2080,7 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1878,32 +2088,32 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1914,7 +2124,7 @@
         <v>24</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1925,40 +2135,40 @@
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -1969,7 +2179,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1980,7 +2190,7 @@
         <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1990,19 +2200,19 @@
       <c r="C19" t="s">
         <v>39</v>
       </c>
-      <c r="D19" t="s">
-        <v>72</v>
+      <c r="D19" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -2012,52 +2222,52 @@
       <c r="C21" t="s">
         <v>44</v>
       </c>
-      <c r="D21" t="s">
-        <v>73</v>
+      <c r="D21" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>49</v>
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>54</v>
+        <v>74</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -2086,10 +2296,10 @@
       <c r="A28" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2111,7 +2321,7 @@
       <c r="C30" t="s">
         <v>89</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="2" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2122,7 +2332,7 @@
       <c r="C31" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="2" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2133,7 +2343,7 @@
       <c r="C32" t="s">
         <v>95</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2144,7 +2354,7 @@
       <c r="C33" t="s">
         <v>98</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="2" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2153,10 +2363,10 @@
         <v>100</v>
       </c>
       <c r="C34" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D34" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -2199,18 +2409,18 @@
       <c r="C38" t="s">
         <v>113</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>115</v>
       </c>
       <c r="C39" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2221,7 +2431,7 @@
       <c r="C40" t="s">
         <v>119</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2232,7 +2442,7 @@
       <c r="C41" t="s">
         <v>122</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2241,10 +2451,10 @@
         <v>124</v>
       </c>
       <c r="C42" t="s">
+        <v>125</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2265,7 +2475,7 @@
       <c r="C44" t="s">
         <v>131</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="2" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2274,10 +2484,10 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
+        <v>135</v>
+      </c>
+      <c r="D45" t="s">
         <v>134</v>
-      </c>
-      <c r="D45" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2292,7 +2502,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>139</v>
       </c>
       <c r="C47" t="s">
@@ -2342,7 +2552,7 @@
       <c r="C51" t="s">
         <v>152</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2364,7 +2574,7 @@
       <c r="C53" t="s">
         <v>158</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2373,10 +2583,10 @@
         <v>160</v>
       </c>
       <c r="C54" t="s">
+        <v>161</v>
+      </c>
+      <c r="D54" t="s">
         <v>162</v>
-      </c>
-      <c r="D54" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -2397,7 +2607,7 @@
       <c r="C56" t="s">
         <v>167</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="7" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2475,29 +2685,29 @@
         <v>188</v>
       </c>
       <c r="D63" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" t="s">
         <v>190</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>191</v>
-      </c>
-      <c r="D64" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>192</v>
+      </c>
+      <c r="C65" t="s">
         <v>193</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>194</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -2519,7 +2729,64 @@
         <v>200</v>
       </c>
       <c r="D67" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>201</v>
+      </c>
+      <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>203</v>
+      </c>
+      <c r="C69" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>205</v>
+      </c>
+      <c r="C70" t="s">
+        <v>206</v>
+      </c>
+      <c r="D70" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>207</v>
+      </c>
+      <c r="C71" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>209</v>
+      </c>
+      <c r="C72" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>212</v>
+      </c>
+      <c r="C73" t="s">
+        <v>213</v>
+      </c>
+      <c r="D73" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE025BDA-48B3-44A6-8949-99F53AA6114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E515C836-ADFD-412C-8C2E-693A65FF24C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="329">
   <si>
     <t>Vocab</t>
   </si>
@@ -2073,13 +2073,655 @@
   </si>
   <si>
     <t>Conj.</t>
+  </si>
+  <si>
+    <t>Dissect</t>
+  </si>
+  <si>
+    <t>Membedah</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">During the advanced literary seminar, the professor instructed the graduate students to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dissect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the author's underlying socio-political commentary rather than merely summarizing the plot</t>
+    </r>
+  </si>
+  <si>
+    <t>Underlying</t>
+  </si>
+  <si>
+    <t>Yang mendasari</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To master advanced calculus, a student must possess a profound comprehension of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>underlying</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mathematical principles that govern limits and continuous functions</t>
+    </r>
+  </si>
+  <si>
+    <t>Possess</t>
+  </si>
+  <si>
+    <t>Mempunyai</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Candidates who </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>possess</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> exceptional analytical capabilities and a high degree of emotional intelligence are far more likely to secure executive positions</t>
+    </r>
+  </si>
+  <si>
+    <t>Profound</t>
+  </si>
+  <si>
+    <t>Mendalam, intens, berbobot</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The technological transition from manual computation to artificial intelligence has exerted a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>profound</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> impact on modern workforce dynamics</t>
+    </r>
+  </si>
+  <si>
+    <t>Comprehension</t>
+  </si>
+  <si>
+    <t>Pemahaman</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reading complex legal documents requires a level of reading </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>comprehension</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that goes beyond merely recognizing vocabulary</t>
+    </r>
+  </si>
+  <si>
+    <t>Superficial</t>
+  </si>
+  <si>
+    <t>Dangkal, tidak mendalam</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>superficial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> analysis of the financial market often leads to erroneous investment decisions during periods of geopolitical instability</t>
+    </r>
+  </si>
+  <si>
+    <t>Yield</t>
+  </si>
+  <si>
+    <t>Imbal hasil, keuntungan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Government bonds currently offer a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>yield</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of 4.5%</t>
+    </r>
+  </si>
+  <si>
+    <t>Menghasilkan, mendatangkan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implementing aggressive fiscal policies may </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>yield</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> short-term economic growth, but it could inadvertently trigger long-term inflationary pressures</t>
+    </r>
+  </si>
+  <si>
+    <t>Rectify</t>
+  </si>
+  <si>
+    <t>Membenahi, meluruskan, memperbaiki</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The software development team worked overnight to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rectify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a critical vulnerability in the source code before the official application launch</t>
+    </r>
+  </si>
+  <si>
+    <t>Scrutinize</t>
+  </si>
+  <si>
+    <t>Memeriksa, menyelidiki, meneliti</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The central bank thoroughly </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scrutinized</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the commercial bank's transaction ledgers to detect any anomalies indicators of illicit money laundering</t>
+    </r>
+  </si>
+  <si>
+    <t>Attempt</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>attempt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to mitigate carbon emissions, the industrial conglomerate invested heavily in renewable energy infrastructures</t>
+    </r>
+  </si>
+  <si>
+    <t>Mencoba, berusaha</t>
+  </si>
+  <si>
+    <t>Discern</t>
+  </si>
+  <si>
+    <t>Melihat, mengenali, membedakan sesuatu yang tidak jelas</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Without statistical tools, it is incredibly difficult to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>discern</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a subtle market trend from random data fluctuations</t>
+    </r>
+  </si>
+  <si>
+    <t>Deceptive</t>
+  </si>
+  <si>
+    <t>Menipu, menyesatkan, memberikan kesan yang salah</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The company’s initial balance sheet looked promising, but it proved to be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deceptive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> upon a closer examination of its cash flow</t>
+    </r>
+  </si>
+  <si>
+    <t>Disguise</t>
+  </si>
+  <si>
+    <t>Menyamarkan, menyembunyikan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sophisticated cybercriminals often </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>disguise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> malicious software as legitimate system updates to bypass corporate firewalls</t>
+    </r>
+  </si>
+  <si>
+    <t>Beneath</t>
+  </si>
+  <si>
+    <t>Di bawah, di balik</t>
+  </si>
+  <si>
+    <r>
+      <t>Beneath</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>the facade of diplomatic cordiality, both nations were actively engaging in covert economic warfare</t>
+    </r>
+  </si>
+  <si>
+    <t>Exceptional</t>
+  </si>
+  <si>
+    <t>Luarbiasa, istimewa</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The researcher demonstrated </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exceptional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> analytical acumen, allows him to resolve mathematical paradoxes that had baffled his peers for decades</t>
+    </r>
+  </si>
+  <si>
+    <t>Capability</t>
+  </si>
+  <si>
+    <t>Kemampuan, potensi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Upgrading the central server's processing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>capability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is paramount if the company intends to deploy large language models in real-time</t>
+    </r>
+  </si>
+  <si>
+    <t>Exert</t>
+  </si>
+  <si>
+    <t>Menggunakan, mengerahkan untuk mencapai sesuatu</t>
+  </si>
+  <si>
+    <t>Require</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Admittance into elite civil service institutions </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>requires</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> candidates to pass a rigorous sequence of standardized logic and psychological examinations</t>
+    </r>
+  </si>
+  <si>
+    <t>Memerlukan, mewajibkan</t>
+  </si>
+  <si>
+    <t>Beyond</t>
+  </si>
+  <si>
+    <t>Di luar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The implications of the newly enacted fiscal policy extend far </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>beyond</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mere short-term market corrections</t>
+    </r>
+  </si>
+  <si>
+    <t>Erroneous</t>
+  </si>
+  <si>
+    <t>Keliru, salah, tidak akurat</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The publication was forced to issue a formal retraction after realizing their article was structured upon </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>erroneous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> statistical data</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2124,6 +2766,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2160,7 +2817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2175,6 +2832,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2479,7 +3137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.6328125" customWidth="1"/>
@@ -2530,1197 +3188,1489 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>229</v>
+      <c r="A4" s="8" t="s">
+        <v>286</v>
       </c>
       <c r="B4" t="s">
         <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s">
-        <v>231</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="B5" t="s">
         <v>228</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="D5" t="s">
-        <v>234</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
         <v>228</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="B7" t="s">
         <v>228</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>240</v>
+        <v>281</v>
+      </c>
+      <c r="D7" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B8" t="s">
         <v>228</v>
       </c>
       <c r="C8" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B9" t="s">
         <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>236</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B10" t="s">
         <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
-      </c>
-      <c r="D10" t="s">
-        <v>248</v>
+        <v>239</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B11" t="s">
         <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D11" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B12" t="s">
         <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D12" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="B13" t="s">
         <v>228</v>
       </c>
       <c r="C13" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="D13" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B14" t="s">
         <v>228</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>218</v>
+        <v>252</v>
       </c>
       <c r="B15" t="s">
         <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
       <c r="B16" t="s">
         <v>228</v>
       </c>
       <c r="C16" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="B17" t="s">
         <v>228</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
       <c r="D17" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
       <c r="D20" t="s">
-        <v>54</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
         <v>261</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
         <v>261</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>263</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
         <v>261</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
         <v>261</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>261</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s">
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>289</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s">
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>226</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s">
         <v>261</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>148</v>
+        <v>292</v>
+      </c>
+      <c r="D31" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="B32" t="s">
         <v>261</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s">
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>301</v>
       </c>
       <c r="D33" t="s">
-        <v>154</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="B34" t="s">
         <v>261</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="B35" t="s">
         <v>261</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s">
         <v>261</v>
       </c>
       <c r="C36" t="s">
-        <v>162</v>
+        <v>275</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="B37" t="s">
         <v>261</v>
       </c>
       <c r="C37" t="s">
-        <v>164</v>
+        <v>141</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B38" t="s">
         <v>261</v>
       </c>
       <c r="C38" t="s">
-        <v>171</v>
-      </c>
-      <c r="D38" t="s">
-        <v>172</v>
+        <v>147</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s">
         <v>261</v>
       </c>
       <c r="C39" t="s">
-        <v>180</v>
-      </c>
-      <c r="D39" t="s">
-        <v>187</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s">
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>185</v>
+        <v>299</v>
       </c>
       <c r="D40" t="s">
-        <v>186</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="D41" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s">
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="D42" t="s">
-        <v>196</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s">
         <v>261</v>
       </c>
       <c r="C43" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="D43" t="s">
-        <v>211</v>
+        <v>296</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>307</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="B46" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="D46" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="B47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="D47" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="B49" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C49" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="B50" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="D51" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="B52" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>34</v>
+        <v>185</v>
+      </c>
+      <c r="D52" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>39</v>
+        <v>189</v>
+      </c>
+      <c r="D53" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>268</v>
       </c>
       <c r="B54" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>65</v>
+        <v>269</v>
+      </c>
+      <c r="D54" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>75</v>
+        <v>195</v>
+      </c>
+      <c r="D55" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="B56" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" t="s">
-        <v>80</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>81</v>
+        <v>210</v>
+      </c>
+      <c r="D56" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="B57" t="s">
         <v>264</v>
       </c>
       <c r="C57" t="s">
-        <v>83</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>84</v>
+        <v>313</v>
+      </c>
+      <c r="D57" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="B58" t="s">
         <v>264</v>
       </c>
       <c r="C58" t="s">
-        <v>108</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>109</v>
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="B59" t="s">
         <v>264</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
         <v>264</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
         <v>264</v>
       </c>
       <c r="C61" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
         <v>264</v>
       </c>
       <c r="C62" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="B63" t="s">
         <v>264</v>
       </c>
       <c r="C63" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="B64" t="s">
         <v>264</v>
       </c>
       <c r="C64" t="s">
-        <v>176</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>183</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>181</v>
+        <v>26</v>
       </c>
       <c r="B65" t="s">
         <v>264</v>
       </c>
       <c r="C65" t="s">
-        <v>182</v>
+        <v>27</v>
+      </c>
+      <c r="D65" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
         <v>264</v>
       </c>
       <c r="C66" t="s">
-        <v>192</v>
-      </c>
-      <c r="D66" t="s">
-        <v>193</v>
+        <v>33</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>197</v>
+        <v>37</v>
       </c>
       <c r="B67" t="s">
         <v>264</v>
       </c>
       <c r="C67" t="s">
-        <v>198</v>
-      </c>
-      <c r="D67" t="s">
-        <v>199</v>
+        <v>38</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="B68" t="s">
         <v>264</v>
       </c>
       <c r="C68" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="D68" t="s">
-        <v>202</v>
+        <v>279</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="B69" t="s">
         <v>264</v>
       </c>
       <c r="C69" t="s">
-        <v>207</v>
-      </c>
-      <c r="D69" t="s">
-        <v>208</v>
+        <v>64</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B70" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" t="s">
-        <v>41</v>
+        <v>74</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="B71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
-      </c>
-      <c r="D71" t="s">
-        <v>44</v>
+        <v>80</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B72" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C72" t="s">
-        <v>67</v>
-      </c>
-      <c r="D72" t="s">
-        <v>68</v>
+        <v>83</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="B73" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C73" t="s">
-        <v>70</v>
-      </c>
-      <c r="D73" t="s">
-        <v>71</v>
+        <v>108</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="B74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C74" t="s">
-        <v>77</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>78</v>
+        <v>115</v>
+      </c>
+      <c r="D74" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="B75" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C75" t="s">
-        <v>87</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>86</v>
+        <v>126</v>
+      </c>
+      <c r="D75" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>134</v>
       </c>
       <c r="B76" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C76" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="D76" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="B77" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C77" t="s">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D77" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="B78" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C78" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="D78" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="B79" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C79" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="D79" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B80" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C80" t="s">
-        <v>174</v>
-      </c>
-      <c r="D80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>177</v>
+        <v>271</v>
       </c>
       <c r="B81" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C81" t="s">
-        <v>178</v>
+        <v>272</v>
+      </c>
+      <c r="D81" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B82" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D82" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B83" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D83" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>215</v>
+        <v>303</v>
       </c>
       <c r="B84" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C84" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="D84" t="s">
-        <v>217</v>
+        <v>305</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="B85" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C85" t="s">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="D85" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>101</v>
+        <v>326</v>
       </c>
       <c r="B86" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C86" t="s">
-        <v>102</v>
+        <v>327</v>
       </c>
       <c r="D86" t="s">
-        <v>103</v>
+        <v>328</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="B87" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C87" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>208</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="D88" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>309</v>
+      </c>
+      <c r="B89" t="s">
+        <v>265</v>
+      </c>
+      <c r="C89" t="s">
+        <v>310</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="s">
+        <v>265</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" t="s">
+        <v>265</v>
+      </c>
+      <c r="C91" t="s">
+        <v>67</v>
+      </c>
+      <c r="D91" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>323</v>
+      </c>
+      <c r="B92" t="s">
+        <v>265</v>
+      </c>
+      <c r="C92" t="s">
+        <v>324</v>
+      </c>
+      <c r="D92" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>69</v>
+      </c>
+      <c r="B93" t="s">
+        <v>265</v>
+      </c>
+      <c r="C93" t="s">
+        <v>70</v>
+      </c>
+      <c r="D93" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>76</v>
+      </c>
+      <c r="B94" t="s">
+        <v>265</v>
+      </c>
+      <c r="C94" t="s">
+        <v>77</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>85</v>
+      </c>
+      <c r="B95" t="s">
+        <v>265</v>
+      </c>
+      <c r="C95" t="s">
+        <v>87</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>88</v>
+      </c>
+      <c r="B96" t="s">
+        <v>265</v>
+      </c>
+      <c r="C96" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>91</v>
+      </c>
+      <c r="B97" t="s">
+        <v>265</v>
+      </c>
+      <c r="C97" t="s">
+        <v>92</v>
+      </c>
+      <c r="D97" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>116</v>
+      </c>
+      <c r="B98" t="s">
+        <v>265</v>
+      </c>
+      <c r="C98" t="s">
+        <v>117</v>
+      </c>
+      <c r="D98" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>137</v>
+      </c>
+      <c r="B99" t="s">
+        <v>265</v>
+      </c>
+      <c r="C99" t="s">
+        <v>138</v>
+      </c>
+      <c r="D99" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>173</v>
+      </c>
+      <c r="B100" t="s">
+        <v>265</v>
+      </c>
+      <c r="C100" t="s">
+        <v>174</v>
+      </c>
+      <c r="D100" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>177</v>
+      </c>
+      <c r="B101" t="s">
+        <v>265</v>
+      </c>
+      <c r="C101" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>203</v>
+      </c>
+      <c r="B102" t="s">
+        <v>265</v>
+      </c>
+      <c r="C102" t="s">
+        <v>204</v>
+      </c>
+      <c r="D102" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>283</v>
+      </c>
+      <c r="B103" t="s">
+        <v>264</v>
+      </c>
+      <c r="C103" t="s">
+        <v>284</v>
+      </c>
+      <c r="D103" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>212</v>
+      </c>
+      <c r="B104" t="s">
+        <v>265</v>
+      </c>
+      <c r="C104" t="s">
+        <v>213</v>
+      </c>
+      <c r="D104" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>215</v>
+      </c>
+      <c r="B105" t="s">
+        <v>265</v>
+      </c>
+      <c r="C105" t="s">
+        <v>216</v>
+      </c>
+      <c r="D105" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>21</v>
+      </c>
+      <c r="B106" t="s">
+        <v>266</v>
+      </c>
+      <c r="C106" t="s">
+        <v>22</v>
+      </c>
+      <c r="D106" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>101</v>
+      </c>
+      <c r="B107" t="s">
+        <v>266</v>
+      </c>
+      <c r="C107" t="s">
+        <v>102</v>
+      </c>
+      <c r="D107" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>104</v>
+      </c>
+      <c r="B108" t="s">
+        <v>266</v>
+      </c>
+      <c r="C108" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>94</v>
+      </c>
+      <c r="B109" t="s">
+        <v>267</v>
+      </c>
+      <c r="C109" t="s">
+        <v>95</v>
+      </c>
+      <c r="D109" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>35</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B110" t="s">
         <v>267</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C110" t="s">
         <v>36</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D110" t="s">
         <v>56</v>
       </c>
     </row>

--- a/daftar_vocab.xlsx
+++ b/daftar_vocab.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\vocab_streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E515C836-ADFD-412C-8C2E-693A65FF24C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEB76D2-6D96-408D-89CF-C907E9BA22DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="384">
   <si>
     <t>Vocab</t>
   </si>
@@ -2714,6 +2714,585 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> statistical data</t>
+    </r>
+  </si>
+  <si>
+    <t>Inheritance</t>
+  </si>
+  <si>
+    <t>Warisan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Although he expected to receive a massive </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>inheritance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> after his grandfather passed away, the complex legal disputes among the family members delayed the distribution of the estate for several years</t>
+    </r>
+  </si>
+  <si>
+    <t>Underpinning</t>
+  </si>
+  <si>
+    <t>Fondasi, basis, dasar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Theoretical physics provides the fundamental </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>underpinning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for many modern technological advancements, even though most consumers rarely think about the science behind their devices</t>
+    </r>
+  </si>
+  <si>
+    <t>Outcomes</t>
+  </si>
+  <si>
+    <t>Hasil</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Before the committee makes its final decision, we must analyze all potential </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>outcomes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> because a single miscalculation could compromise the entire project</t>
+    </r>
+  </si>
+  <si>
+    <t>Web</t>
+  </si>
+  <si>
+    <t>Jaring, jaringan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The detective spent months untangling the intricate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of deceit that the corrupt officials had created to hide their financial crimes</t>
+    </r>
+  </si>
+  <si>
+    <t>Compound</t>
+  </si>
+  <si>
+    <t>Memperbanyak</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If you do not address these minor errors immediately, they will </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compound</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> over time until the entire system breaks down completely.</t>
+    </r>
+  </si>
+  <si>
+    <t>Praise</t>
+  </si>
+  <si>
+    <t>Memuji</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">he headmaster publicly </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>praised</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the students who organized the charity event because their dedication brought significant financial aid to the local orphanage.</t>
+    </r>
+  </si>
+  <si>
+    <t>Foreclose</t>
+  </si>
+  <si>
+    <t>Menyita</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Because the homeowner failed to pay his mortgage for six consecutive months, the bank decided to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>foreclose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on the property before the winter settled in.</t>
+    </r>
+  </si>
+  <si>
+    <t>Thrill</t>
+  </si>
+  <si>
+    <t>Mendatangkan sensasi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roller coasters </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thrill</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> millions of amusement park visitors every year, even though the intense speed and steep drops can terrify others</t>
+    </r>
+  </si>
+  <si>
+    <t>Outperform</t>
+  </si>
+  <si>
+    <t>Menungguli</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Our new software application is expected to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>outperform</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> all its competitors on the market because it uses a highly optimized processing algorithm</t>
+    </r>
+  </si>
+  <si>
+    <t>Coexsist</t>
+  </si>
+  <si>
+    <t>Hidup berdampingan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In a truly multicultural society, diverse traditions can </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>coexist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> harmoniously as long as citizens maintain mutual respect for each other’s beliefs</t>
+    </r>
+  </si>
+  <si>
+    <t>Delve</t>
+  </si>
+  <si>
+    <t>Menyelam, menggali secara dalam, menganalisis</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Before you write your thesis, you need to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>delve</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> into historical archives so that your arguments are backed by reliable primary sources</t>
+    </r>
+  </si>
+  <si>
+    <t>Empower</t>
+  </si>
+  <si>
+    <t>Memberdayakan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The new leadership program aims to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>empower</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> young executives so that they can confidently make critical strategic decisions for the company's future</t>
+    </r>
+  </si>
+  <si>
+    <t>Align</t>
+  </si>
+  <si>
+    <t>Menyelaraskan, menyejajarkan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We need to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>align</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> our marketing strategies with current consumer trends if we want to maximize our sales figures this quarter</t>
+    </r>
+  </si>
+  <si>
+    <t>Recognize</t>
+  </si>
+  <si>
+    <t>Mengenali, menyadari, mengakui</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Although she disguised herself perfectly for the masquerade ball, her closest friends managed to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>recognize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> her voice almost instantly.</t>
+    </r>
+  </si>
+  <si>
+    <t>Unconscious</t>
+  </si>
+  <si>
+    <t>Dilakukan secara tidak sadar</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Many of our daily habits are driven by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unconscious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> desires that we rarely analyze or question in our waking hours</t>
+    </r>
+  </si>
+  <si>
+    <t>Deliberate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adj. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The actor made a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deliberate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> choice to avoid the media because he wanted to keep his personal life completely private</t>
+    </r>
+  </si>
+  <si>
+    <t>Sengaja, terencana, dilakukan dengan penuh pertimbangan</t>
+  </si>
+  <si>
+    <t>Allegedly</t>
+  </si>
+  <si>
+    <t>Berdasarkan dugaan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The politician </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>allegedly</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> accepted bribes from the corporation, although no concrete evidence has been presented in court yet</t>
+    </r>
+  </si>
+  <si>
+    <t>Skillfully</t>
+  </si>
+  <si>
+    <t>Dengan mahir</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">She </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>skillfully</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> navigated the political discussion without offending any of the guests, which proved her exceptional diplomatic talent</t>
     </r>
   </si>
 </sst>
@@ -2817,7 +3396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2832,7 +3411,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3137,7 +3715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D128"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.6328125" customWidth="1"/>
@@ -3174,1503 +3752,1755 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>98</v>
+      <c r="A3" t="s">
+        <v>329</v>
       </c>
       <c r="B3" t="s">
         <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>330</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>286</v>
+      <c r="A4" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B4" t="s">
         <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>288</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="B5" t="s">
         <v>228</v>
       </c>
       <c r="C5" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="D5" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>315</v>
       </c>
       <c r="B6" t="s">
         <v>228</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>316</v>
       </c>
       <c r="D6" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>332</v>
       </c>
       <c r="B7" t="s">
         <v>228</v>
       </c>
       <c r="C7" t="s">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="D7" t="s">
-        <v>282</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>338</v>
       </c>
       <c r="B8" t="s">
         <v>228</v>
       </c>
       <c r="C8" t="s">
-        <v>233</v>
+        <v>339</v>
       </c>
       <c r="D8" t="s">
-        <v>234</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s">
         <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>335</v>
       </c>
       <c r="B10" t="s">
         <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>240</v>
+        <v>336</v>
+      </c>
+      <c r="D10" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="B11" t="s">
         <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="D11" t="s">
-        <v>243</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B12" t="s">
         <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>233</v>
+      </c>
+      <c r="D12" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B13" t="s">
         <v>228</v>
       </c>
       <c r="C13" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B14" t="s">
         <v>228</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
-      </c>
-      <c r="D14" t="s">
-        <v>251</v>
+        <v>239</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B15" t="s">
         <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="D15" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="B16" t="s">
         <v>228</v>
       </c>
       <c r="C16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
         <v>228</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="D17" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="B18" t="s">
         <v>228</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="B19" t="s">
         <v>228</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="B20" t="s">
         <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="D20" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C22" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>225</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>222</v>
       </c>
       <c r="D24" t="s">
-        <v>55</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
         <v>261</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>286</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>227</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s">
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>289</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>291</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
         <v>261</v>
       </c>
       <c r="C31" t="s">
-        <v>292</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>227</v>
       </c>
       <c r="B32" t="s">
         <v>261</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="B33" t="s">
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="D33" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>128</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s">
         <v>261</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>360</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>365</v>
       </c>
       <c r="B35" t="s">
         <v>261</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>366</v>
       </c>
       <c r="D35" t="s">
-        <v>133</v>
+        <v>367</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="B36" t="s">
         <v>261</v>
       </c>
       <c r="C36" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="D36" t="s">
-        <v>276</v>
+        <v>370</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s">
         <v>261</v>
       </c>
       <c r="C37" t="s">
-        <v>141</v>
+        <v>342</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>146</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s">
         <v>261</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>148</v>
+        <v>345</v>
+      </c>
+      <c r="D38" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>318</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>261</v>
       </c>
       <c r="C39" t="s">
-        <v>319</v>
-      </c>
-      <c r="D39" s="7"/>
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>297</v>
+        <v>119</v>
       </c>
       <c r="B40" t="s">
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>299</v>
+        <v>120</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>149</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s">
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>357</v>
       </c>
       <c r="D41" t="s">
-        <v>151</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s">
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="D42" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>294</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s">
         <v>261</v>
       </c>
       <c r="C43" t="s">
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="D43" t="s">
-        <v>296</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>152</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s">
         <v>261</v>
       </c>
       <c r="C44" t="s">
-        <v>153</v>
+        <v>292</v>
       </c>
       <c r="D44" t="s">
-        <v>154</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s">
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="B46" t="s">
         <v>261</v>
       </c>
       <c r="C46" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D46" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="B47" t="s">
         <v>261</v>
       </c>
       <c r="C47" t="s">
-        <v>159</v>
+        <v>301</v>
       </c>
       <c r="D47" t="s">
-        <v>160</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="B48" t="s">
         <v>261</v>
       </c>
       <c r="C48" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="B49" t="s">
         <v>261</v>
       </c>
       <c r="C49" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>274</v>
       </c>
       <c r="B50" t="s">
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>171</v>
+        <v>275</v>
       </c>
       <c r="D50" t="s">
-        <v>172</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="B51" t="s">
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="B52" t="s">
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>185</v>
-      </c>
-      <c r="D52" t="s">
-        <v>186</v>
+        <v>147</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>188</v>
+        <v>318</v>
       </c>
       <c r="B53" t="s">
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>189</v>
-      </c>
-      <c r="D53" t="s">
-        <v>190</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="B54" t="s">
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D54" t="s">
-        <v>270</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>194</v>
+        <v>149</v>
       </c>
       <c r="B55" t="s">
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="D55" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>209</v>
+        <v>320</v>
       </c>
       <c r="B56" t="s">
         <v>261</v>
       </c>
       <c r="C56" t="s">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="D56" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B57" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C57" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="D57" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C58" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="B59" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>9</v>
+        <v>307</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>308</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>155</v>
       </c>
       <c r="B60" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="B61" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="D61" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="B62" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>19</v>
+        <v>163</v>
       </c>
       <c r="B63" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C63" t="s">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="D63" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
       <c r="B64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="B65" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
       <c r="D65" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
       <c r="B66" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C66" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>34</v>
+        <v>185</v>
+      </c>
+      <c r="D66" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
       <c r="B67" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>38</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>39</v>
+        <v>189</v>
+      </c>
+      <c r="D67" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B68" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C68" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D68" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>194</v>
       </c>
       <c r="B69" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>65</v>
+        <v>195</v>
+      </c>
+      <c r="D69" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="B70" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>75</v>
+        <v>210</v>
+      </c>
+      <c r="D70" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>79</v>
+        <v>312</v>
       </c>
       <c r="B71" t="s">
         <v>264</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>81</v>
+        <v>313</v>
+      </c>
+      <c r="D71" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="B72" t="s">
         <v>264</v>
       </c>
       <c r="C72" t="s">
-        <v>83</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>84</v>
+        <v>5</v>
+      </c>
+      <c r="D72" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="B73" t="s">
         <v>264</v>
       </c>
       <c r="C73" t="s">
-        <v>108</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>109</v>
+        <v>9</v>
+      </c>
+      <c r="D73" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="B74" t="s">
         <v>264</v>
       </c>
       <c r="C74" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="D74" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="B75" t="s">
         <v>264</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>134</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
         <v>264</v>
       </c>
       <c r="C76" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="B77" t="s">
         <v>264</v>
       </c>
       <c r="C77" t="s">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="D77" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
         <v>264</v>
       </c>
       <c r="C78" t="s">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="D78" t="s">
-        <v>168</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>175</v>
+        <v>26</v>
       </c>
       <c r="B79" t="s">
         <v>264</v>
       </c>
       <c r="C79" t="s">
-        <v>176</v>
+        <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>183</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>181</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
         <v>264</v>
       </c>
       <c r="C80" t="s">
-        <v>182</v>
+        <v>33</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>271</v>
+        <v>37</v>
       </c>
       <c r="B81" t="s">
         <v>264</v>
       </c>
       <c r="C81" t="s">
-        <v>272</v>
-      </c>
-      <c r="D81" t="s">
-        <v>273</v>
+        <v>38</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>191</v>
+        <v>277</v>
       </c>
       <c r="B82" t="s">
         <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="D82" t="s">
-        <v>193</v>
+        <v>279</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>197</v>
+        <v>371</v>
       </c>
       <c r="B83" t="s">
         <v>264</v>
       </c>
       <c r="C83" t="s">
-        <v>198</v>
+        <v>372</v>
       </c>
       <c r="D83" t="s">
-        <v>199</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>303</v>
+        <v>374</v>
       </c>
       <c r="B84" t="s">
-        <v>264</v>
+        <v>375</v>
       </c>
       <c r="C84" t="s">
-        <v>304</v>
+        <v>377</v>
       </c>
       <c r="D84" t="s">
-        <v>305</v>
+        <v>376</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="B85" t="s">
         <v>264</v>
       </c>
       <c r="C85" t="s">
-        <v>201</v>
-      </c>
-      <c r="D85" t="s">
-        <v>202</v>
+        <v>64</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>326</v>
+        <v>73</v>
       </c>
       <c r="B86" t="s">
         <v>264</v>
       </c>
       <c r="C86" t="s">
-        <v>327</v>
-      </c>
-      <c r="D86" t="s">
-        <v>328</v>
+        <v>74</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>206</v>
+        <v>79</v>
       </c>
       <c r="B87" t="s">
         <v>264</v>
       </c>
       <c r="C87" t="s">
-        <v>207</v>
-      </c>
-      <c r="D87" t="s">
-        <v>208</v>
+        <v>80</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="B88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C88" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" t="s">
-        <v>41</v>
+        <v>83</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>309</v>
+        <v>107</v>
       </c>
       <c r="B89" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C89" t="s">
-        <v>310</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>311</v>
+        <v>108</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="B90" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C90" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="B91" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C91" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="D91" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>323</v>
+        <v>134</v>
       </c>
       <c r="B92" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C92" t="s">
-        <v>324</v>
+        <v>135</v>
       </c>
       <c r="D92" t="s">
-        <v>325</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="B93" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C93" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="D93" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="B94" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C94" t="s">
-        <v>77</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>78</v>
+        <v>167</v>
+      </c>
+      <c r="D94" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C95" t="s">
-        <v>87</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>86</v>
+        <v>176</v>
+      </c>
+      <c r="D95" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C96" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>91</v>
+        <v>271</v>
       </c>
       <c r="B97" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C97" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="D97" t="s">
-        <v>93</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>116</v>
+        <v>191</v>
       </c>
       <c r="B98" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C98" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="D98" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="B99" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C99" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="D99" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>173</v>
+        <v>303</v>
       </c>
       <c r="B100" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C100" t="s">
-        <v>174</v>
+        <v>304</v>
       </c>
       <c r="D100" t="s">
-        <v>183</v>
+        <v>305</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="B101" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C101" t="s">
-        <v>178</v>
+        <v>201</v>
+      </c>
+      <c r="D101" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>203</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>327</v>
       </c>
       <c r="D102" t="s">
-        <v>205</v>
+        <v>328</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="B103" t="s">
         <v>264</v>
       </c>
       <c r="C103" t="s">
-        <v>284</v>
+        <v>207</v>
       </c>
       <c r="D103" t="s">
-        <v>285</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>212</v>
+        <v>6</v>
       </c>
       <c r="B104" t="s">
         <v>265</v>
       </c>
       <c r="C104" t="s">
-        <v>213</v>
+        <v>7</v>
       </c>
       <c r="D104" t="s">
-        <v>214</v>
+        <v>41</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>215</v>
+        <v>309</v>
       </c>
       <c r="B105" t="s">
         <v>265</v>
       </c>
       <c r="C105" t="s">
-        <v>216</v>
-      </c>
-      <c r="D105" t="s">
-        <v>217</v>
+        <v>310</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C106" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="B107" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C107" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="D107" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>104</v>
+        <v>323</v>
       </c>
       <c r="B108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C108" t="s">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="D108" t="s">
-        <v>106</v>
+        <v>325</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="B109" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C109" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D109" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
+        <v>76</v>
+      </c>
+      <c r="B110" t="s">
+        <v>265</v>
+      </c>
+      <c r="C110" t="s">
+        <v>77</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>381</v>
+      </c>
+      <c r="B111" t="s">
+        <v>265</v>
+      </c>
+      <c r="C111" t="s">
+        <v>382</v>
+      </c>
+      <c r="D111" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>85</v>
+      </c>
+      <c r="B112" t="s">
+        <v>265</v>
+      </c>
+      <c r="C112" t="s">
+        <v>87</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>88</v>
+      </c>
+      <c r="B113" t="s">
+        <v>265</v>
+      </c>
+      <c r="C113" t="s">
+        <v>89</v>
+      </c>
+      <c r="D113" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>378</v>
+      </c>
+      <c r="B114" t="s">
+        <v>265</v>
+      </c>
+      <c r="C114" t="s">
+        <v>379</v>
+      </c>
+      <c r="D114" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>91</v>
+      </c>
+      <c r="B115" t="s">
+        <v>265</v>
+      </c>
+      <c r="C115" t="s">
+        <v>92</v>
+      </c>
+      <c r="D115" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" t="s">
+        <v>265</v>
+      </c>
+      <c r="C116" t="s">
+        <v>117</v>
+      </c>
+      <c r="D116" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>137</v>
+      </c>
+      <c r="B117" t="s">
+        <v>265</v>
+      </c>
+      <c r="C117" t="s">
+        <v>138</v>
+      </c>
+      <c r="D117" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>173</v>
+      </c>
+      <c r="B118" t="s">
+        <v>265</v>
+      </c>
+      <c r="C118" t="s">
+        <v>174</v>
+      </c>
+      <c r="D118" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>177</v>
+      </c>
+      <c r="B119" t="s">
+        <v>265</v>
+      </c>
+      <c r="C119" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>203</v>
+      </c>
+      <c r="B120" t="s">
+        <v>265</v>
+      </c>
+      <c r="C120" t="s">
+        <v>204</v>
+      </c>
+      <c r="D120" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>283</v>
+      </c>
+      <c r="B121" t="s">
+        <v>264</v>
+      </c>
+      <c r="C121" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>212</v>
+      </c>
+      <c r="B122" t="s">
+        <v>265</v>
+      </c>
+      <c r="C122" t="s">
+        <v>213</v>
+      </c>
+      <c r="D122" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>215</v>
+      </c>
+      <c r="B123" t="s">
+        <v>265</v>
+      </c>
+      <c r="C123" t="s">
+        <v>216</v>
+      </c>
+      <c r="D123" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>21</v>
+      </c>
+      <c r="B124" t="s">
+        <v>266</v>
+      </c>
+      <c r="C124" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>101</v>
+      </c>
+      <c r="B125" t="s">
+        <v>266</v>
+      </c>
+      <c r="C125" t="s">
+        <v>102</v>
+      </c>
+      <c r="D125" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>104</v>
+      </c>
+      <c r="B126" t="s">
+        <v>266</v>
+      </c>
+      <c r="C126" t="s">
+        <v>105</v>
+      </c>
+      <c r="D126" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>94</v>
+      </c>
+      <c r="B127" t="s">
+        <v>267</v>
+      </c>
+      <c r="C127" t="s">
+        <v>95</v>
+      </c>
+      <c r="D127" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>35</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B128" t="s">
         <v>267</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C128" t="s">
         <v>36</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D128" t="s">
         <v>56</v>
       </c>
     </row>
